--- a/光伏配储项目/电价数据/2026/礼乐站.xlsx
+++ b/光伏配储项目/电价数据/2026/礼乐站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5347000000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.20852</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.63822</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9819500000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.80018</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.70448</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44005</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45586</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44052</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42263</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42239</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44552</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.46299</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.73148</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.59201</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.48512</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.5346799999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.5604</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.24731</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.76759</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.76858</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.7631599999999999</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.46305</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.1445</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.50842</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.50496</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.76967</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.56408</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.62215</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.60577</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.76652</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.71496</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.76655</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.00028</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.30067</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.44019</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.65957</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.6421699999999999</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.13837</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.94602</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.8078200000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.95751</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.14163</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.9208999999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.64741</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.70121</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.37529</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.12496</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.71139</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.06356</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.17743</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.03486</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.38366</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.14979</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.13999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.09808</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.71224</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47935</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42216</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.05639</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9494600000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.02576</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53612</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5350199999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49785</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47238</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42097</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.54588</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.74697</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7239800000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45771</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44002</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.81345</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.9520299999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.58917</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.76415</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.81189</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.6976100000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.61958</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.47822</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.49847</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6060599999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.99942</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.02706</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.30981</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.95829</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.20881</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.84499</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.77962</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.17368</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.99048</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.8764999999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.41805</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.48476</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.57498</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46882</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.49144</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.08289</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.92262</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.88506</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.9117999999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8265800000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.74952</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.76906</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.48061</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.8623500000000001</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.04983</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.02068</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.8428</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.23005</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.45873</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.39673</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.44993</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.54815</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.53179</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.69692</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.07568</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.17706</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.76575</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.89946</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.64727</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.61854</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7741399999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44073</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43474</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33349</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51547</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.46169</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5381699999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43001</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4351</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41474</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44953</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47331</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.61034</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.6176799999999999</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.76671</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.6276</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.5847899999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.59212</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.47752</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.68057</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.87578</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.20814</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.59414</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.95026</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.26081</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.78439</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.8272200000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.66273</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7848999999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.92377</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.90667</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.66214</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.44204</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.5006700000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.8864</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.83277</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.92887</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.45064</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.09975</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.93428</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.87888</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.82176</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.23472</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.10367</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.06267</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.08123</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.05661</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.0026</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.4768</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.8853</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.4903</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.8826900000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9035700000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.88963</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.97615</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.9050199999999999</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.00692</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.84537</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.65638</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.64166</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.49167</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.88261</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.57433</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.47971</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.46194</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.51187</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.56824</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.5524600000000001</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46645</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.56299</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.52976</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.64358</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.87091</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.9246</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.6451</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.99621</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.04661</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.61521</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.7031499999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.97656</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.93789</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.15328</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.81941</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.85748</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.5236000000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.64716</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.47173</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.5159400000000001</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.79126</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.94567</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.7620800000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.79344</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.8300299999999999</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.77093</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.7366699999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.70062</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.90454</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.94962</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.58225</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.9157799999999999</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.61776</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.78962</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.83594</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.7689</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.85925</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.93762</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9525800000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.92761</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.94948</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.54414</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.87699</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.83912</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.79137</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.8572799999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.88974</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.8863</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.85878</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.8069299999999999</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.5825199999999999</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.5900700000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31054</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.54883</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.19662</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.26929</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.20386</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.21894</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15985</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.15574</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.15651</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.27104</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.22706</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.18662</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.20184</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.19299</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.19269</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.14511</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.16164</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.17665</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.15333</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.28533</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.49705</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.49265</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.44672</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40985</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31071</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.98942</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.7455700000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.77506</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.52522</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.50946</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.21508</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06356000000000001</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.15171</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04411</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04432</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04187</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00644</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19845</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04586</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.13977</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.05322</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04277</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04474</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.01713</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04199</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.15018</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04443</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04238</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.15063</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.15274</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.16242</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.16842</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.16875</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.17083</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33592</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3828</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.24742</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.23996</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.26913</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.59729</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.7017</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.5548500000000001</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.52825</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.57911</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.62574</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.76715</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48162</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.45845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.62239</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.72287</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.49888</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.45643</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14303</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.58321</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.5347000000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.5291</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.65384</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79614</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.72838</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.53264</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.65931</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.93921</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.24191</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.72525</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.26105</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.23294</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.6508</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.6522899999999999</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.22248</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.9031</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.60173</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.22017</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.63673</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.62706</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.31091</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.70065</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80452</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7876000000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7883300000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88097</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50586</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41627</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46448</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22337</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63927</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54239</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45261</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59449</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43316</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.58575</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66523</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.78647</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.55711</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55668</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5348999999999999</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.25194</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8550399999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.12726</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.10488</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.0746</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.46374</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.62713</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.46546</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.51595</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.74051</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.65079</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.54863</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.49815</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.7744800000000001</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.64875</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.28979</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.51924</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.5307200000000001</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.50187</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.49435</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.51875</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.53842</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.49298</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.5160800000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.5292899999999999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.48786</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.51202</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.50517</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.5271</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.60788</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.51686</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.6015499999999999</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.5295599999999999</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.5247999999999999</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.5367999999999999</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.5170800000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.50544</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.49338</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.50131</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.43913</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.46333</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35307</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9558300000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47615</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47808</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54038</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.5568500000000001</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.47197</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.50732</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.5791799999999999</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.6792999999999999</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.82992</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.65754</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.7649900000000001</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.6528400000000001</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.72576</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.66374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.52926</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.6329900000000001</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.7615499999999999</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.41243</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.6846599999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.07351</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5634199999999999</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.89198</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.62614</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.63851</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.51424</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.10655</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.59358</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.43369</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.47721</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.76966</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.06117</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.70839</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.34888</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70355</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7953</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.68823</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.6144299999999999</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.67993</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.8531599999999999</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.69943</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.52704</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.03952</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.5558999999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.04515</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.36236</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.94226</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.10028</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.6875399999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.48212</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.13309</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.9983300000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.79904</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.78187</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.75687</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.7978200000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.19025</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.00674</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.48229</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.63705</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.9870399999999999</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.57385</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.78635</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.7644299999999999</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.66135</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.70353</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.6851699999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.82164</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.83496</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.6829</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.84458</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.09766</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.7697000000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.76695</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.85507</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.73188</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.7524999999999999</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.07458</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.7431</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.75493</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.82389</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.70594</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.69356</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.28336</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.86805</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.4363</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.18668</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.78035</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.78308</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.63047</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3247</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.26555</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.7136699999999999</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.65813</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.25402</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.27691</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25866</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46867</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.42591</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.54916</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.28442</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.51759</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.47055</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.56613</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.7569900000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.7128099999999999</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.57382</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.52124</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.62441</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.73062</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.72094</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.59823</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.54528</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.67198</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.67401</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.66273</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.6650499999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.9430499999999999</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.94001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.60445</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.71861</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.0995</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.64554</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.08367</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.96376</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.9564900000000001</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.02386</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.75749</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.17344</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.7483500000000001</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.72685</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.65596</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.95609</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.93916</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.97258</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.98593</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.98105</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.9581900000000001</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.98264</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.76027</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.01578</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.20651</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.09716</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.10984</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.01273</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.02047</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.02856</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.96801</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.06284</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.6534</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.7089</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.00656</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.01493</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.00883</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.51064</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.08825</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.40507</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.03845</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.16612</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.58625</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.50326</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.55392</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.0527</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.68602</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32113</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.42113</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.71108</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.58348</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.5411699999999999</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.62182</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.88628</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.75813</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.61513</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.5374099999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.41162</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.43513</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39287</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3493</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.54014</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.02612</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5629299999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.5284800000000001</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6519199999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83092</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47181</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.55347</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.5299400000000001</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.60484</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.16507</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.25242</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.25938</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.50935</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.69917</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.65095</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.94109</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.7676900000000001</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.26542</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.6226499999999999</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.7681399999999999</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.57086</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.8005099999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.7497200000000001</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.6067100000000001</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.15545</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.69029</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.88127</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5299299999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.9805700000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.57689</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.9006799999999999</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.06899</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.8643999999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.64512</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.1111</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.9242400000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.67794</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41131</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41828</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5604199999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.0784</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.55208</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.63289</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.70601</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.43903</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.38972</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.56578</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.41263</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.45051</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.5214800000000001</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.72213</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.72139</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.7899700000000001</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.28196</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.7489</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.60303</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.34711</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.28747</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.20829</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.1123</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.8052699999999999</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.71538</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.05986</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.43884</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.43831</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.48859</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.50676</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.62246</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.87314</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.5868099999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.74821</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.57063</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.76598</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.76214</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.21775</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.17612</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.8961</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.89725</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.02857</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.02862</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.38262</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.48035</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.07808</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.16538</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.68259</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.68433</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.9134099999999999</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.09998</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.8025599999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47802</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4714100000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.99634</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6074700000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4823</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45803</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.44821</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4905</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.45295</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.59148</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.56633</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.5689099999999999</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.91283</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.83856</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.18481</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.07911</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.66142</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.70799</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.45898</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.48005</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.44708</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43657</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.46799</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.46852</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.43806</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4275</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.49877</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.47988</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.53865</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36414</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.62538</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.80491</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.5194800000000001</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43113</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.17848</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27041</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.17454</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.26081</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.18736</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.22478</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.23696</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.26709</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.51287</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43843</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.48917</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44148</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35168</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.57092</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25462</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.39541</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.22953</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.22178</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.18032</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.24734</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.16209</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.17849</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.15913</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.2059</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.49404</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.23701</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.21386</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.17153</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.16183</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.15428</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.16122</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.18087</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.15343</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.16138</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.15345</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.16537</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.16124</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.16253</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.26402</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.20153</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27194</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.62103</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.30419</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.80879</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.80702</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.47366</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.52859</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.4974</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.59604</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.53716</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.88822</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.89125</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.00915</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85512</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.66555</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.90804</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05420000000000001</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.43809</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21055</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.16154</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.16869</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.65332</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.49225</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.45148</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.75935</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.35626</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.5962499999999999</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.52644</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.90073</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.71121</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.71192</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.7192799999999999</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.72693</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.85541</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5405599999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.75735</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.57399</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.78328</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.17823</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.17892</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.21293</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.60091</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.1787</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.27089</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.3432</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.70291</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8988400000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.75919</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.80874</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.80632</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.10409</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.9539</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.74678</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.57562</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33671</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.47233</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.61963</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.46246</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.57773</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5786</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.46343</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25512</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.85853</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.70909</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.64401</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.60029</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5634600000000001</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.51542</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.49802</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.75118</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.8759</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.7884500000000001</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.87873</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.20299</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.19765</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.79953</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.81741</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.5824199999999999</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.44897</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.22833</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.45362</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.51555</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.02497</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.6591</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.44728</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.46806</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.47314</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.53901</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.8617400000000001</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.5384800000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.46857</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.97115</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.67116</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5733200000000001</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.86125</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.70797</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.45708</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.46059</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.44832</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.45694</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33859</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42597</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.4104100000000001</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.5236499999999999</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58699</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.54828</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.80301</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.04188</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.43936</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.66536</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.64239</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.75701</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.7957799999999999</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.74427</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.71696</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.75076</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.7294299999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.71866</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.7218300000000001</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.1144</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.46174</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.72523</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.7322000000000001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.54568</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.71404</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.60229</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.7265900000000001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.70508</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.73041</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.98978</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.14465</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.16719</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.21456</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.28131</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.26436</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.33417</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.34663</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.32453</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.95278</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.84641</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.81096</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47925</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.01347</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.78242</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.86661</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.7405900000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.68099</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.6672</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.6689700000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.6389400000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68533</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5459700000000001</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40176</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45846</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.5680499999999999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.63549</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.59942</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.67265</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.44461</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.68688</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.55748</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.69525</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.61451</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.61622</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.52999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.54031</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.55968</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.7992899999999999</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.65232</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.79814</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.7286900000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.80616</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.78895</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.7890900000000001</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.0169</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.03583</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.76589</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.49801</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.56996</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.59726</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.67538</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.65838</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.69497</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.15789</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.16002</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.46443</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.18087</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.46807</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.44971</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.48169</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.28625</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.21091</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.88229</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.86282</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.51067</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.58411</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.28251</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.28384</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.10624</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.49736</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.58803</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.56371</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.04298</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.99434</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.7450399999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.25273</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.2311</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.50751</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.27441</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.27619</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.64996</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.6321599999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.61713</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37506</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27079</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.57666</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.44032</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.5614400000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.8357599999999999</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.67395</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.60376</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.63014</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.80303</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.8090900000000001</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.9490299999999999</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.53425</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.25654</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.9988400000000001</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.94957</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.6233300000000001</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.43591</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15209</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.53853</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.28422</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.6140399999999999</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.21363</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.61678</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.7024600000000001</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.6076</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.7114299999999999</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.50704</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.8116599999999999</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.6564099999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.7307100000000001</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.59301</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.72384</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.8094</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.86472</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.72778</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.73881</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.71629</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.7202799999999999</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.73089</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.09224</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.13646</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.03115</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.05027</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.22073</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.98354</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.01313</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.78961</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.7700399999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.78501</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.82367</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.82326</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.80455</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.9152899999999999</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.60545</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.5806399999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.52576</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.50581</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37535</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.27876</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.87117</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.90015</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.15535</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.73788</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.61153</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.49313</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.58096</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.58048</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.5472899999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.69033</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.5867</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.6958200000000001</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.21387</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.73594</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.80291</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.90225</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.8904299999999999</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.78964</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.9970599999999999</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.7517999999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.42642</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.12127</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.7625299999999999</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.50286</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.7695700000000001</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.57739</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.43049</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.50962</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.01364</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.82104</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.57008</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.22893</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.8117000000000001</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.80668</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.30502</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.21555</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.03112</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.86779</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.83141</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.84197</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.84009</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.86591</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.86458</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.89507</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.28843</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.32952</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.42199</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.79364</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.81862</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.84113</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.81899</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.86402</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.01913</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.60721</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.58461</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.47594</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.9534199999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.62212</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.62395</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.43367</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.69216</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.54167</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.80243</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.06673</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.75964</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.80102</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.51178</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.48757</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.45752</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.33648</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.9091699999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.63544</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.54813</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.48671</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.6428400000000001</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.50903</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.42181</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.82076</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.69638</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.70652</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.73409</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.56192</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.53846</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.5234800000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.5371699999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.54348</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.55916</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.6231599999999999</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.62849</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.52586</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.62259</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.62942</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.89999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.6607499999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.56911</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.57298</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.5561200000000001</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.52022</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.6520900000000001</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.62949</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.6772100000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.55947</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.51991</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47136</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
